--- a/data/incremental/incremental_06_nunoa_manual.xlsx
+++ b/data/incremental/incremental_06_nunoa_manual.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -460,7 +460,7 @@
     <col width="15" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="36" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,7 +664,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/%C2%A1Ay+mi+Madre!+Restobar+Plaza+%C3%91u%C3%B1oa/@-33.4536316,-70.5936559,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cfd02d008955:0x95e3c1a6b2a42343!8m2!3d-33.4536316!4d-70.5936559!16s%2Fg%2F11ms539982?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/%C2%A1Ay+mi+Madre!+Restobar+Plaza+%C3%91u%C3%B1oa/data=!4m7!3m6!1s0x9662cfd02d008955:0x95e3c1a6b2a42343!8m2!3d-33.4536316!4d-70.5936559!16s%2Fg%2F11ms539982!19sChIJVYkALdDPYpYRQyOksqbB45U?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,32 +938,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Restaurante Peruano ENTRE MAR Y TIERRA</t>
+          <t>Kechua Restaurant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pedro de Ona 031, 8320000 Ñuñoa, Región Metropolitana</t>
+          <t>Alcaldesa Balbina Vera 3561, Local 102, 7750000 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9 6463 6426</t>
+          <t>(2) 2401 7556</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>http://www.entre-marytierra.cl/</t>
+          <t>https://kechuarestaurantes.cl/nunoa/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Peruano+ENTRE+MAR+Y+TIERRA/@-33.4539742,-70.629641,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c55d8a478a83:0x4cdbaaa649b8affb!8m2!3d-33.4539742!4d-70.629641!16s%2Fg%2F11rmsyns_f?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Kechua+Restaurant/data=!4m7!3m6!1s0x9662cfb0f4386de5:0xb5c7a28854d2fa9d!8m2!3d-33.4538533!4d-70.5937068!16s%2Fg%2F11tnm645sj!19sChIJ5W049LDPYpYRnfrSVIiix7U?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.4539742</t>
+          <t>-33.4538533</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-70.629641</t>
+          <t>-70.5937068</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1041,32 +1041,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kechua Restaurant</t>
+          <t>Restaurante Peruano ENTRE MAR Y TIERRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>318</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alcaldesa Balbina Vera 3561, Local 102, 7750000 Ñuñoa, Región Metropolitana</t>
+          <t>Pedro de Ona 031, 8320000 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(2) 2401 7556</t>
+          <t>9 6463 6426</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://kechuarestaurantes.cl/nunoa/</t>
+          <t>http://www.entre-marytierra.cl/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Kechua+Restaurant/data=!4m7!3m6!1s0x9662cfb0f4386de5:0xb5c7a28854d2fa9d!8m2!3d-33.4538533!4d-70.5937068!16s%2Fg%2F11tnm645sj!19sChIJ5W049LDPYpYRnfrSVIiix7U?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+Peruano+ENTRE+MAR+Y+TIERRA/data=!4m7!3m6!1s0x9662c55d8a478a83:0x4cdbaaa649b8affb!8m2!3d-33.4539742!4d-70.629641!16s%2Fg%2F11rmsyns_f!19sChIJg4pHil3FYpYR-6-4Saaq20w?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-33.4538533</t>
+          <t>-33.4539742</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-70.5937068</t>
+          <t>-70.629641</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1144,34 +1144,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>La Finestra</t>
+          <t>Como en Lima</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>626</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Av. Irarrázaval 3465, 7790825 Ñuñoa, Región Metropolitana</t>
+          <t>Manuel de Salas 71, 7790570 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(2) 2205 4502</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>http://www.lafinestra.cl/</t>
-        </is>
-      </c>
+          <t>(2) 2209 8867</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -1179,17 +1175,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Finestra/data=!4m7!3m6!1s0x9662cfbef8dd4c6d:0xe6916fd1306cf3d4!8m2!3d-33.4553941!4d-70.5948372!16s%2Fg%2F1tfmdfmx!19sChIJbUzd-L7PYpYR1PNsMNFvkeY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Como+en+Lima/data=!4m7!3m6!1s0x9662cfbec3166451:0x5bacdff36b13c56!8m2!3d-33.4545639!4d-70.5931006!16s%2Fg%2F11cn9mz9v4!19sChIJUWQWw77PYpYRVjyxNv_NugU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.4553941</t>
+          <t>-33.4545639</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-70.5948372</t>
+          <t>-70.5931006</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1214,12 +1210,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1247,30 +1243,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Como en Lima</t>
+          <t>La Finestra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Manuel de Salas 71, 7790570 Ñuñoa, Región Metropolitana</t>
+          <t>Av. Irarrázaval 3465, 7790825 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(2) 2209 8867</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>(2) 2205 4502</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>http://www.lafinestra.cl/</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Como+en+Lima/data=!4m7!3m6!1s0x9662cfbec3166451:0x5bacdff36b13c56!8m2!3d-33.4545639!4d-70.5931006!16s%2Fg%2F11cn9mz9v4!19sChIJUWQWw77PYpYRVjyxNv_NugU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/La+Finestra/data=!4m7!3m6!1s0x9662cfbef8dd4c6d:0xe6916fd1306cf3d4!8m2!3d-33.4553941!4d-70.5948372!16s%2Fg%2F1tfmdfmx!19sChIJbUzd-L7PYpYR1PNsMNFvkeY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-33.4545639</t>
+          <t>-33.4553941</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-70.5931006</t>
+          <t>-70.5948372</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Punto+Pa%C3%ADs+Restaurant/@-33.4492307,-70.5965692,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cfbd41051cef:0x6c5bb104ce58f86!8m2!3d-33.4492307!4d-70.5965692!16s%2Fg%2F11f1zlnj_7?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Punto+Pa%C3%ADs+Restaurant/data=!4m7!3m6!1s0x9662cfbd41051cef:0x6c5bb104ce58f86!8m2!3d-33.4492307!4d-70.5965692!16s%2Fg%2F11f1zlnj_7!19sChIJ7xwFQb3PYpYRho_lTBC7xQY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>751</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Moray/@-33.4490363,-70.6241282,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c59bf408de7f:0xf0bcf121cfe7e8ce!8m2!3d-33.4490363!4d-70.6241282!16s%2Fg%2F11pcrq1qlp?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+Moray/data=!4m7!3m6!1s0x9662c59bf408de7f:0xf0bcf121cfe7e8ce!8m2!3d-33.4490363!4d-70.6241282!16s%2Fg%2F11pcrq1qlp!19sChIJf94I9JvFYpYRzujnzyHxvPA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Antonia+Lounge/@-33.453623,-70.5933652,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf1795ab37af:0x26f0848757404258!8m2!3d-33.453623!4d-70.5933652!16s%2Fg%2F11sbhtqq6_?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Antonia+Lounge/data=!4m7!3m6!1s0x9662cf1795ab37af:0x26f0848757404258!8m2!3d-33.453623!4d-70.5933652!16s%2Fg%2F11sbhtqq6_!19sChIJrzerlRfPYpYRWEJAV4eE8CY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>794</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1861,52 +1861,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Golfo Di Napoli Trattoria e Pizzeria</t>
+          <t>Peyo Restaurant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dublé Almeyda 2435, 7750147 Ñuñoa, Región Metropolitana</t>
+          <t>Lo Encalada 465, 7750200 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(2) 2341 3675</t>
+          <t>(2) 2506 4758</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://golfodinapoli.cl/</t>
+          <t>https://peyo.cl/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Restaurante italiano</t>
+          <t>Restaurante chileno</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Golfo+Di+Napoli+Trattoria+e+Pizzeria/data=!4m7!3m6!1s0x9662cf916f827eaf:0x65a6a856994a5153!8m2!3d-33.455948!4d-70.605786!16s%2Fg%2F1tj1nqnk!19sChIJr36Cb5HPYpYRU1FKmVaopmU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Peyo+Restaurant/data=!4m7!3m6!1s0x9662c5624b4feab9:0x3d815e7e459c8d2e!8m2!3d-33.456417!4d-70.6249084!16s%2Fg%2F1hjh8m92r!19sChIJuepPS2LFYpYRLo2cRX5egT0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.455948</t>
+          <t>-33.456417</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-70.605786</t>
+          <t>-70.6249084</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1964,52 +1964,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peyo Restaurant</t>
+          <t>Las Lanzas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lo Encalada 465, 7750200 Ñuñoa, Región Metropolitana</t>
+          <t>Humberto Trucco 25, 7790825 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(2) 2506 4758</t>
+          <t>(2) 2225 5589</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://peyo.cl/</t>
+          <t>https://www.facebook.com/Las-Lanzas-Restaurant-y-Fuente-de-Soda-17409706655/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Peyo+Restaurant/@-33.456417,-70.6249084,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c5624b4feab9:0x3d815e7e459c8d2e!8m2!3d-33.456417!4d-70.6249084!16s%2Fg%2F1hjh8m92r?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Las+Lanzas/data=!4m7!3m6!1s0x9662cf12e26cfa4f:0xe640e0e62fb2f985!8m2!3d-33.4555253!4d-70.5942732!16s%2Fg%2F11g1lwc7x9!19sChIJT_ps4hLPYpYRhfmyL-bgQOY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.456417</t>
+          <t>-33.4555253</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-70.6249084</t>
+          <t>-70.5942732</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2067,52 +2067,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Las Lanzas</t>
+          <t>Golfo Di Napoli Trattoria e Pizzeria</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Humberto Trucco 25, 7790825 Ñuñoa, Región Metropolitana</t>
+          <t>Dublé Almeyda 2435, 7750147 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(2) 2225 5589</t>
+          <t>(2) 2341 3675</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Las-Lanzas-Restaurant-y-Fuente-de-Soda-17409706655/</t>
+          <t>https://golfodinapoli.cl/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante italiano</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Las+Lanzas/@-33.4555253,-70.5942732,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf12e26cfa4f:0xe640e0e62fb2f985!8m2!3d-33.4555253!4d-70.5942732!16s%2Fg%2F11g1lwc7x9?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Golfo+Di+Napoli+Trattoria+e+Pizzeria/data=!4m7!3m6!1s0x9662cf916f827eaf:0x65a6a856994a5153!8m2!3d-33.455948!4d-70.605786!16s%2Fg%2F1tj1nqnk!19sChIJr36Cb5HPYpYRU1FKmVaopmU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.4555253</t>
+          <t>-33.455948</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-70.5942732</t>
+          <t>-70.605786</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Terraza+Vergel/@-33.4490585,-70.624408,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c5c15107efe9:0xdd9265eded43ee4c!8m2!3d-33.4490585!4d-70.624408!16s%2Fg%2F11kj0530d4?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Terraza+Vergel/data=!4m7!3m6!1s0x9662c5c15107efe9:0xdd9265eded43ee4c!8m2!3d-33.4490585!4d-70.624408!16s%2Fg%2F11kj0530d4!19sChIJ6e8HUcHFYpYRTO5D7e1lkt0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>220</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2582,52 +2582,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>La casa del curanto</t>
+          <t>Good Restaurante</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>395</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dublé Almeyda 2779, 7750169 Ñuñoa, Región Metropolitana</t>
+          <t>José Domingo Cañas 1917, 7750000 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9 2855 3749</t>
+          <t>(2) 2261 6101</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lacasadelcuranto?igshid=MmVlMjlkMTBhMg==</t>
+          <t>https://www.instagram.com/goodrestaurante/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Restaurante de comida para llevar</t>
+          <t>Bar restaurante</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+casa+del+curanto/data=!4m7!3m6!1s0x9662cf0045cd8d8f:0xdb11e68502065073!8m2!3d-33.4560782!4d-70.6021461!16s%2Fg%2F11y2bx1rn5!19sChIJj43NRQDPYpYRc1AGAoXmEds?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Good+Restaurante/data=!4m7!3m6!1s0x9662cf8dea275df5:0x460e3f9a8a62dd7b!8m2!3d-33.4567244!4d-70.611154!16s%2Fg%2F11ckj6x78n!19sChIJ9V0n6o3PYpYRe91iipo_DkY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.4560782</t>
+          <t>-33.4567244</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-70.6021461</t>
+          <t>-70.611154</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2680,16 +2680,12 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>Revisar: parece comida para llevar</t>
-        </is>
-      </c>
+      <c r="AG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Abbatia Casona Restaurant</t>
+          <t>Las Vegas Chile Sandwichería</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2699,22 +2695,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>727</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Av. Campos de Deportes 329, 7750126 Ñuñoa, Región Metropolitana</t>
+          <t>Av. José Pedro Alessandri 2014, 7800280 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9 3893 2224</t>
+          <t>(2) 2567 6417</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://abbatiarestaurant.ola.click/</t>
+          <t>http://www.lasvegaschile.com/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2724,17 +2720,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Abbatia+Casona+Restaurant/data=!4m7!3m6!1s0x9662cf05615f4f63:0x9766ecdf65522666!8m2!3d-33.4564871!4d-70.6095265!16s%2Fg%2F11rjjvb7j5!19sChIJY09fYQXPYpYRZiZSZd_sZpc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Las+Vegas+Chile+Sandwicher%C3%ADa/data=!4m7!3m6!1s0x9662cfe77aad036b:0xfbe8119d10f79eed!8m2!3d-33.4731665!4d-70.598517!16s%2Fg%2F11bwfk5w7v!19sChIJawOteufPYpYR7Z73EJ0R6Ps?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.4564871</t>
+          <t>-33.4731665</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-70.6095265</t>
+          <t>-70.598517</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2759,7 +2755,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2787,57 +2783,61 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Revisar: parece sandwich</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Restaurante Warique</t>
+          <t>Tapas y Birra Ñuñoa - Restaurante Mediterráneo &amp; Bar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>José Domingo Cañas 1879, 7750000 Ñuñoa, Región Metropolitana</t>
+          <t>Alcaldesa Balbina Vera 3561, 7790884 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(2) 2341 1495</t>
+          <t>(2) 2904 1230</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>http://warique.cl/</t>
+          <t>http://www.tapasybirra.cl/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante mediterráneo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Warique/data=!4m7!3m6!1s0x9662cf8dc4d9b1e5:0xab46c3f5ef0fac4d!8m2!3d-33.4566764!4d-70.6116943!16s%2Fg%2F11bwydc2dt!19sChIJ5bHZxI3PYpYRTawP7_XDRqs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Tapas+y+Birra+%C3%91u%C3%B1oa+-+Restaurante+Mediterr%C3%A1neo+%26+Bar/data=!4m7!3m6!1s0x9662cfbe944f9dc3:0xad1467f8fc07cf6a!8m2!3d-33.4538497!4d-70.5935726!16s%2Fg%2F11c0vn_jvx!19sChIJw51PlL7PYpYRas8H_PhnFK0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.4566764</t>
+          <t>-33.4538497</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-70.6116943</t>
+          <t>-70.5935726</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2895,48 +2895,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mr. Sabroso Restaurant</t>
+          <t>Kigo Vegan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>168</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Condell 1701, 7770331 Santiago, Ñuñoa, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>José Manuel Infante 2452, 7750000 Ñuñoa, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(2) 2608 0919</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>http://mrsabroso.cl/</t>
+          <t>https://www.kigovegan.cl/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bar restaurante</t>
+          <t>Restaurante vegano</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mr.+Sabroso+Restaurant/data=!4m7!3m6!1s0x9662c5fcff776ced:0xbe068199878f51ef!8m2!3d-33.4502879!4d-70.6251398!16s%2Fg%2F11t8g9tb3q!19sChIJ7Wx3__zFYpYR71GPh5mBBr4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Kigo+Vegan/data=!4m7!3m6!1s0x9662cf3ce939b133:0x7e6fa0b834e3889a!8m2!3d-33.4533509!4d-70.6175634!16s%2Fg%2F11sgl8n27x!19sChIJM7E56TzPYpYRmojjNLigb34?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.4502879</t>
+          <t>-33.4533509</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-70.6251398</t>
+          <t>-70.6175634</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2961,12 +2965,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2989,57 +2993,57 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shawarmas Chile Nuñoa</t>
+          <t>Restaurante El Puro Perú - Ñuñoa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Av. Irarrázaval 1822, 7501173 Ñuñoa, Región Metropolitana</t>
+          <t>Av. José Pedro Alessandri 1809, 7780266 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9 9412 3085</t>
+          <t>(2) 2401 9290</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://linktr.ee/shawarmas_chile</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>https://www.elpuroperu.cl/</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Restaurante peruano</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Shawarmas+Chile+Nu%C3%B1oa/data=!4m7!3m6!1s0x9662cfea36ee092d:0x359a13b5db25fcd2!8m2!3d-33.4531813!4d-70.6119221!16s%2Fg%2F11wj9s0xxt!19sChIJLQnuNurPYpYR0vwl27UTmjU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+El+Puro+Per%C3%BA+-+%C3%91u%C3%B1oa/data=!4m7!3m6!1s0x9662cfe79328fab7:0x57668c28e06b33c9!8m2!3d-33.4712431!4d-70.5988422!16s%2Fg%2F11fy_r_9ll!19sChIJt_ook-fPYpYRyTNr4CiMZlc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.4531813</t>
+          <t>-33.4712431</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-70.6119221</t>
+          <t>-70.5988422</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3064,7 +3068,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3074,7 +3078,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R25" t="inlineStr"/>
@@ -3097,52 +3101,48 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Perú Mágico Tenedor Libre</t>
+          <t>Plaza Ñuñoa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Av. Pedro de Valdivia 3323, 7750000 Ñuñoa, Región Metropolitana</t>
+          <t>Manuel de Salas 71, 7750000 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(2) 2344 4493</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://perumagicotenedorlibre.cl/</t>
-        </is>
-      </c>
+          <t>(2) 2204 5224</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Parque</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Per%C3%BA+M%C3%A1gico+Tenedor+Libre/@-33.4529922,-70.6051114,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf913be1a3eb:0x94f2dd1238d82af2!8m2!3d-33.4529922!4d-70.6051114!16s%2Fg%2F12lsdt9lg?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Plaza+%C3%91u%C3%B1oa/data=!4m7!3m6!1s0x9662cfbf04ab4a7b:0x5a99e4565277755f!8m2!3d-33.4560843!4d-70.5937153!16s%2Fm%2F0n_650x!19sChIJe0qrBL_PYpYRX3V3UlbkmVo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.4529922</t>
+          <t>-33.4560843</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-70.6051114</t>
+          <t>-70.5937153</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3167,17 +3167,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
@@ -3200,32 +3200,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TierraLibre restaurante y panadería</t>
+          <t>Abbatia Casona Restaurant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>405</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Miguel Claro 2220, 7750000 Ñuñoa, Región Metropolitana</t>
+          <t>Av. Campos de Deportes 329, 7750126 Ñuñoa, Región Metropolitana</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>9 9309 4223</t>
+          <t>9 3893 2224</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>http://www.pantierralibre.cl/</t>
+          <t>https://abbatiarestaurant.ola.click/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/TierraLibre+restaurante+y+panader%C3%ADa/data=!4m7!3m6!1s0x9662cf5d210aafb3:0x75c5fb8a496fa6bf!8m2!3d-33.4487734!4d-70.6161701!16s%2Fg%2F11m_jfmj9g!19sChIJs68KIV3PYpYRv6ZvSYr7xXU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Abbatia+Casona+Restaurant/data=!4m7!3m6!1s0x9662cf05615f4f63:0x9766ecdf65522666!8m2!3d-33.4564871!4d-70.6095265!16s%2Fg%2F11rjjvb7j5!19sChIJY09fYQXPYpYRZiZSZd_sZpc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.4487734</t>
+          <t>-33.4564871</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-70.6161701</t>
+          <t>-70.6095265</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R27" t="inlineStr"/>
@@ -3298,14 +3298,410 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>Revisar: parece panaderia</t>
-        </is>
-      </c>
+      <c r="AG27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Clasico el Dante</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Av. Irarrázaval 3482, 7790827 Ñuñoa, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>9 6469 8510</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bar restaurante</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Clasico+el+Dante/data=!4m7!3m6!1s0x9662cfbefa2e9bc5:0x1e1d7ddf3baebe0a!8m2!3d-33.455137!4d-70.5945072!16s%2Fg%2F11bztvjjb9!19sChIJxZsu-r7PYpYRCr6uO999HR4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-33.455137</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-70.5945072</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Restaurante Donde Camilo</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Zañartu 2530, 7780293 Ñuñoa, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>9 8555 0970</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurante peruano</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Restaurante+Donde+Camilo/data=!4m7!3m6!1s0x9662cfe59b11b6ed:0x1dc2ab007fd761ee!8m2!3d-33.4719429!4d-70.6061339!16s%2Fg%2F1tm89n3z!19sChIJ7bYRm-XPYpYR7mHXfwCrwh0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-33.4719429</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-70.6061339</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mr. Sabroso Restaurant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Condell 1701, 7770331 Santiago, Ñuñoa, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>http://mrsabroso.cl/</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bar restaurante</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Mr.+Sabroso+Restaurant/data=!4m7!3m6!1s0x9662c5fcff776ced:0xbe068199878f51ef!8m2!3d-33.4502879!4d-70.6251398!16s%2Fg%2F11t8g9tb3q!19sChIJ7Wx3__zFYpYR71GPh5mBBr4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-33.4502879</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-70.6251398</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>El Manzano</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Av. Irarrázaval 3285, Ñuñoa, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(2) 2225 5145</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/El+Manzano/data=!4m7!3m6!1s0x9662cfbe391474a5:0xe54d2597533bdca7!8m2!3d-33.4553092!4d-70.5967223!16s%2Fg%2F1tvw63qr!19sChIJpXQUOb7PYpYRp9w7U5clTeU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-33.4553092</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-70.5967223</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG27"/>
+  <autoFilter ref="A1:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>